--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="C2" t="n">
         <v>4.2</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="C3" t="n">
         <v>3.4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="4">
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
         <v>3.3</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="C5" t="n">
         <v>3.1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="6">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="C6" t="n">
         <v>3.5</v>
       </c>
       <c r="D6" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="7">
@@ -538,7 +538,7 @@
         <v>3.8</v>
       </c>
       <c r="D7" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="8">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="C9" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="10">

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="C2" t="n">
         <v>4.2</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="C3" t="n">
         <v>3.4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="4">
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
         <v>3.3</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="C5" t="n">
         <v>3.1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="6">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="C6" t="n">
         <v>3.5</v>
       </c>
       <c r="D6" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="7">
@@ -538,7 +538,7 @@
         <v>3.8</v>
       </c>
       <c r="D7" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="8">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="C9" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="10">
@@ -608,7 +608,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -618,12 +618,142 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>CWcwKOO8</t>
+          <t>QekfJmLa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vJDNK0d4</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WhAFMMRi</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ChPK4l66</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>CWcwKOO8</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="C3" t="n">
         <v>3.4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="4">
@@ -596,13 +596,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
         <v>3.4</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="12">
@@ -628,7 +628,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>ng6idLW1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -638,122 +638,12 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>CWcwKOO8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>OQqSjnv9</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>YcAFQVSP</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>IVonL9jm</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>hA5zaJZp</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>MNr3HRkC</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>ChPK4l66</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>hpMqQeYq</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>4KmdZaBc</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>8CpDVHAM</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>ng6idLW1</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>CWcwKOO8</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
         <v>3.1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="6">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="C6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D6" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="C7" t="n">
         <v>3.8</v>
       </c>
       <c r="D7" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="8">
@@ -628,7 +628,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -638,12 +638,82 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>CWcwKOO8</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>CWcwKOO8</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,187 +448,199 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hO0nKEm3</t>
+          <t>ITdtTrn2</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="C2" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>QyafIhIF</t>
+          <t>E1Xs9lu2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="C3" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="C4" t="n">
         <v>3.3</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
+          <t>QekfJmLa</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="C5" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="D5" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ruUIA1G6</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="C6" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.25</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
         <v>4.75</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
+          <t>OQqSjnv9</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.55</v>
+        <v>3.5</v>
       </c>
       <c r="C8" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="D8" t="n">
-        <v>7.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
+          <t>YcAFQVSP</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.75</v>
+        <v>2.35</v>
       </c>
       <c r="C9" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.55</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ITdtTrn2</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.4</v>
+        <v>1.14</v>
       </c>
       <c r="C10" t="n">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>3.2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>E1Xs9lu2</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="C11" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="D11" t="n">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8KIT2SzJ</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>QekfJmLa</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+          <t>ChPK4l66</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.75</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -638,7 +650,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -648,7 +660,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>8CpDVHAM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -658,7 +670,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -668,7 +680,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -678,7 +690,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -688,7 +700,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -698,7 +710,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -708,12 +720,132 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>CWcwKOO8</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>YN50iYWr</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>CWcwKOO8</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,257 +448,311 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hO0nKEm3</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="C2" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>QyafIhIF</t>
+          <t>QekfJmLa</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="C3" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="C4" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>1.62</v>
       </c>
       <c r="C5" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>2.55</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ruUIA1G6</t>
+          <t>OQqSjnv9</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.73</v>
+        <v>3.5</v>
       </c>
       <c r="C6" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="D6" t="n">
-        <v>5.25</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
+          <t>YcAFQVSP</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.75</v>
+        <v>2.35</v>
       </c>
       <c r="C7" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.55</v>
+        <v>1.13</v>
       </c>
       <c r="C8" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="D8" t="n">
-        <v>7.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.75</v>
+        <v>2.35</v>
       </c>
       <c r="C9" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.55</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ITdtTrn2</t>
+          <t>MNr3HRkC</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="C10" t="n">
         <v>3.1</v>
       </c>
       <c r="D10" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>E1Xs9lu2</t>
+          <t>ChPK4l66</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1.62</v>
       </c>
       <c r="C11" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>2.35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8KIT2SzJ</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.25</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>QekfJmLa</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.45</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.67</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>0Y1WIvRG</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5.8</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>f92vnwe3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t>KhwykQ8L</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="D17" t="n">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>v1KiOZ2d</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5.6</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+          <t>CQ0ABdJj</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5.4</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+          <t>0ns5XwtA</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -708,12 +762,112 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>CWcwKOO8</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>YN50iYWr</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>CWcwKOO8</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,7 +474,7 @@
         <v>3.6</v>
       </c>
       <c r="D3" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="4">
@@ -848,26 +848,6 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>ng6idLW1</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>CWcwKOO8</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,406 +448,66 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8KIT2SzJ</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="C2" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>QekfJmLa</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="C3" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>OQqSjnv9</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="C4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="D4" t="n">
-        <v>3.25</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>YcAFQVSP</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.62</v>
+        <v>2.45</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>OQqSjnv9</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="C6" t="n">
         <v>3.2</v>
       </c>
-      <c r="D6" t="n">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>YcAFQVSP</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>IVonL9jm</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="C8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>hA5zaJZp</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>MNr3HRkC</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>ChPK4l66</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="C11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>hpMqQeYq</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="D12" t="n">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>4KmdZaBc</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8CpDVHAM</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>0Y1WIvRG</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D15" t="n">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>f92vnwe3</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>KhwykQ8L</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="C17" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="D17" t="n">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>v1KiOZ2d</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="D18" t="n">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>CQ0ABdJj</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="C19" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="D19" t="n">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>0ns5XwtA</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="C20" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>OlferefS</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>SM0npHPF</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>GOO6q4Wr</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>xhKUdf9L</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>EJYZzDn2</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>tQQLbGv9</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,66 +448,310 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.45</v>
+        <v>1.17</v>
       </c>
       <c r="C2" t="n">
-        <v>3.1</v>
+        <v>7.5</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="C3" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>MNr3HRkC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.9</v>
+        <v>2.45</v>
       </c>
       <c r="C4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>ChPK4l66</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2</v>
-      </c>
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>0Y1WIvRG</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>f92vnwe3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>KhwykQ8L</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>v1KiOZ2d</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CQ0ABdJj</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>0ns5XwtA</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>YN50iYWr</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,215 +448,191 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.17</v>
+        <v>1.9</v>
       </c>
       <c r="C2" t="n">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2.25</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>8CpDVHAM</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.45</v>
+        <v>4.5</v>
       </c>
       <c r="C4" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ChPK4l66</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="C5" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="D5" t="n">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hpMqQeYq</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="C6" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4KmdZaBc</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="C7" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="D7" t="n">
-        <v>3.4</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8CpDVHAM</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.5</v>
+        <v>1.65</v>
       </c>
       <c r="C8" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="C9" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="D9" t="n">
-        <v>6.25</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="D10" t="n">
-        <v>3.25</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="C11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>9.5</v>
-      </c>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>5.5</v>
-      </c>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>CQ0ABdJj</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="C13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>5.25</v>
-      </c>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>7</v>
-      </c>
-      <c r="C14" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.4</v>
-      </c>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -666,7 +642,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -676,7 +652,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -686,7 +662,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -696,7 +672,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -706,52 +682,12 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,246 +448,258 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hpMqQeYq</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="C2" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4KmdZaBc</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="C3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8CpDVHAM</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="C4" t="n">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="C5" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="D5" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="C6" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.33</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>9.5</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="C8" t="n">
-        <v>3.5</v>
+        <v>5.75</v>
       </c>
       <c r="D8" t="n">
-        <v>5.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CQ0ABdJj</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="C9" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="D9" t="n">
-        <v>5.25</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>2.63</v>
       </c>
       <c r="C10" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.63</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
           <t>YN50iYWr</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="B17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="C17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,257 +448,161 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8</v>
+        <v>6.25</v>
       </c>
       <c r="D2" t="n">
-        <v>5.75</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="C4" t="n">
-        <v>5.25</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.62</v>
+        <v>2.6</v>
       </c>
       <c r="C5" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>CQ0ABdJj</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.7</v>
+        <v>2.75</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="D6" t="n">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>1.91</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="D7" t="n">
-        <v>1.38</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="C8" t="n">
-        <v>5.75</v>
+        <v>3.25</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D9" t="n">
         <v>2.8</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="C10" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="D10" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.4</v>
+        <v>1.29</v>
       </c>
       <c r="C11" t="n">
-        <v>3.1</v>
+        <v>5.75</v>
       </c>
       <c r="D11" t="n">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>EJYZzDn2</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2.63</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>tQQLbGv9</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="C17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,160 +448,80 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="C2" t="n">
-        <v>6.25</v>
+        <v>3.5</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="C3" t="n">
         <v>3.25</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.75</v>
+        <v>1.29</v>
       </c>
       <c r="C6" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>tQQLbGv9</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="C10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2.38</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="C11" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="D11" t="n">
         <v>9.5</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,81 +448,161 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>YeqTho8m</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="C2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D2" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
+          <t>08zpk37C</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="C3" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>n1v9mjW7</t>
+          <t>CjIFsr1e</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="C4" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h4pRxZHk</t>
+          <t>8EcB5Oig</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="C5" t="n">
         <v>2.9</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YN50iYWr</t>
+          <t>jckS1tiI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.29</v>
+        <v>3.75</v>
       </c>
       <c r="C6" t="n">
-        <v>5.75</v>
+        <v>3.6</v>
       </c>
       <c r="D6" t="n">
-        <v>9.5</v>
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SfxxiPx0</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>na927pNt</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>dzUhmsxP</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>SdHeBgOE</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fVeJ32M5</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="C2" t="n">
         <v>3.6</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="3">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="C5" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="6">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="C6" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="D6" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="7">
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="C7" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="D7" t="n">
         <v>5</v>
@@ -551,10 +551,10 @@
         <v>4.1</v>
       </c>
       <c r="C8" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="D8" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="C9" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="D9" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="10">
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="C10" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -596,14 +596,192 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="C11" t="n">
         <v>3.1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.8</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>AyPaTn1c</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>8b5vHIeT</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>xjut9IFr</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IRBb0lXA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>dYbQEmn4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4b2YCRGG</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xWrPG9Hi</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ImLNuMV7</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>dCNk2A2b</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>OAmz0KLU</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>pxdwg6Pp</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>QiF6bS1N</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,340 +448,98 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>YeqTho8m</t>
+          <t>SfxxiPx0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="C2" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="D2" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>08zpk37C</t>
+          <t>na927pNt</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.45</v>
+        <v>4.33</v>
       </c>
       <c r="C3" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.88</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CjIFsr1e</t>
+          <t>dzUhmsxP</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.63</v>
+        <v>3.8</v>
       </c>
       <c r="C4" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8EcB5Oig</t>
+          <t>SdHeBgOE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.25</v>
+        <v>1.33</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>jckS1tiI</t>
+          <t>fVeJ32M5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2</v>
+        <v>2.05</v>
       </c>
       <c r="C6" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>AyPaTn1c</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="C7" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>na927pNt</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>dzUhmsxP</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.05</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>SdHeBgOE</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="C10" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="D10" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>fVeJ32M5</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>AyPaTn1c</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>8b5vHIeT</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>xjut9IFr</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>IRBb0lXA</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>dYbQEmn4</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>4b2YCRGG</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>xWrPG9Hi</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>ImLNuMV7</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>dCNk2A2b</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>OAmz0KLU</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>pxdwg6Pp</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>QiF6bS1N</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>445r4WXo</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>rkN7RQV9</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>bwZsTw7E</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>f5SjRHyR</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,98 +448,438 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>AyPaTn1c</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.67</v>
+        <v>2.9</v>
       </c>
       <c r="C2" t="n">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>na927pNt</t>
+          <t>8b5vHIeT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.33</v>
+        <v>1.91</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>1.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dzUhmsxP</t>
+          <t>xjut9IFr</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="C4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SdHeBgOE</t>
+          <t>IRBb0lXA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fVeJ32M5</t>
+          <t>dYbQEmn4</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.05</v>
+        <v>3.75</v>
       </c>
       <c r="C6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>AyPaTn1c</t>
+          <t>4b2YCRGG</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>xWrPG9Hi</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>2.75</v>
       </c>
-      <c r="C7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="C8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ImLNuMV7</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="C9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>dCNk2A2b</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C10" t="n">
         <v>2.8</v>
       </c>
+      <c r="D10" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OAmz0KLU</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pxdwg6Pp</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>QiF6bS1N</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C17" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="D17" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ddsD5q9j</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>QDjsB5oT</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>bqbA3PNE</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>6VWd5zF7</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>pGrl7dpe</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>06X4YYrf</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>hMoEUjrJ</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>KSw0hfzQ</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>YemQuHjK</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>4vvdzeEs</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>h0AwIDbD</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>jyEMLeal</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>4rQsoH7m</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>n37VJZT0</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>YJVCWCD6</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,438 +448,146 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AyPaTn1c</t>
+          <t>dYbQEmn4</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.9</v>
+        <v>4.33</v>
       </c>
       <c r="C2" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8b5vHIeT</t>
+          <t>4b2YCRGG</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>xjut9IFr</t>
+          <t>xWrPG9Hi</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="C4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="D4" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>IRBb0lXA</t>
+          <t>ImLNuMV7</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1.17</v>
       </c>
       <c r="C5" t="n">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>4.1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dYbQEmn4</t>
+          <t>dCNk2A2b</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.75</v>
+        <v>2.05</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="D6" t="n">
-        <v>2.15</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4b2YCRGG</t>
+          <t>OAmz0KLU</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>xWrPG9Hi</t>
+          <t>pxdwg6Pp</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="D8" t="n">
-        <v>2.55</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ImLNuMV7</t>
+          <t>QiF6bS1N</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.17</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>dCNk2A2b</t>
+          <t>445r4WXo</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="C10" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="D10" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>OAmz0KLU</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>pxdwg6Pp</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="C12" t="n">
-        <v>4</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>QiF6bS1N</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>445r4WXo</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D14" t="n">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>rkN7RQV9</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D15" t="n">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>bwZsTw7E</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>f5SjRHyR</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="C17" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="D17" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>ddsD5q9j</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D18" t="n">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>QDjsB5oT</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="C19" t="n">
-        <v>5</v>
-      </c>
-      <c r="D19" t="n">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>bqbA3PNE</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="C20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2.05</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>6VWd5zF7</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="C21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>pGrl7dpe</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="C22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2.05</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>06X4YYrf</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>hMoEUjrJ</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>KSw0hfzQ</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>YemQuHjK</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>4vvdzeEs</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>h0AwIDbD</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>jyEMLeal</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>4rQsoH7m</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>n37VJZT0</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>YJVCWCD6</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,98 +448,406 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>445r4WXo</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="C2" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>na927pNt</t>
+          <t>rkN7RQV9</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.33</v>
+        <v>1.7</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="D3" t="n">
-        <v>1.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dzUhmsxP</t>
+          <t>bwZsTw7E</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="C4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SdHeBgOE</t>
+          <t>f5SjRHyR</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="C5" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fVeJ32M5</t>
+          <t>ddsD5q9j</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="C6" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>AyPaTn1c</t>
+          <t>QDjsB5oT</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.75</v>
+        <v>1.25</v>
       </c>
       <c r="C7" t="n">
-        <v>2.88</v>
+        <v>6.25</v>
       </c>
       <c r="D7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>bqbA3PNE</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>6VWd5zF7</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>pGrl7dpe</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>06X4YYrf</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>2.8</v>
       </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>hMoEUjrJ</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>KSw0hfzQ</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>YemQuHjK</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>4vvdzeEs</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>h0AwIDbD</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>jyEMLeal</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>4rQsoH7m</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>n37VJZT0</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>YJVCWCD6</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>QmPfsURO</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>0AJjqex0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>40FWnYcm</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>KApUeTtI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>EB22wLQj</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>CQIvoCSa</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>4Ef51XCt</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>hzRnqjcC</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>YgnMckC5</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>CvbDaBsg</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,406 +448,130 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>445r4WXo</t>
+          <t>rkN7RQV9</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="D2" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rkN7RQV9</t>
+          <t>bwZsTw7E</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="C3" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bwZsTw7E</t>
+          <t>f5SjRHyR</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="C4" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="D4" t="n">
-        <v>3.75</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>f5SjRHyR</t>
+          <t>ddsD5q9j</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.2</v>
+        <v>1.73</v>
       </c>
       <c r="C5" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ddsD5q9j</t>
+          <t>QDjsB5oT</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="C6" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>QDjsB5oT</t>
+          <t>bqbA3PNE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.25</v>
+        <v>3.25</v>
       </c>
       <c r="C7" t="n">
-        <v>6.25</v>
+        <v>3.5</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bqbA3PNE</t>
+          <t>6VWd5zF7</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="C8" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>6VWd5zF7</t>
+          <t>pGrl7dpe</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="C9" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>pGrl7dpe</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.95</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>06X4YYrf</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>hMoEUjrJ</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>KSw0hfzQ</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
         <v>1.91</v>
       </c>
-      <c r="C13" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" t="n">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>YemQuHjK</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D14" t="n">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>4vvdzeEs</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>7</v>
-      </c>
-      <c r="C15" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>h0AwIDbD</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>jyEMLeal</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D17" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>4rQsoH7m</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D18" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>n37VJZT0</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>YJVCWCD6</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="C20" t="n">
-        <v>4</v>
-      </c>
-      <c r="D20" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>QmPfsURO</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>0AJjqex0</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>40FWnYcm</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>KApUeTtI</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>EB22wLQj</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>CQIvoCSa</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>4Ef51XCt</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>hzRnqjcC</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>YgnMckC5</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>CvbDaBsg</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,406 +448,146 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>445r4WXo</t>
+          <t>06X4YYrf</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="D2" t="n">
-        <v>5.25</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rkN7RQV9</t>
+          <t>hMoEUjrJ</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="C3" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bwZsTw7E</t>
+          <t>KSw0hfzQ</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="C4" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>f5SjRHyR</t>
+          <t>YemQuHjK</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.2</v>
+        <v>1.85</v>
       </c>
       <c r="C5" t="n">
-        <v>6.5</v>
+        <v>3.25</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ddsD5q9j</t>
+          <t>4vvdzeEs</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.73</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="D6" t="n">
-        <v>4.5</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>QDjsB5oT</t>
+          <t>h0AwIDbD</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="C7" t="n">
-        <v>6.25</v>
+        <v>3.6</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bqbA3PNE</t>
+          <t>jyEMLeal</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.25</v>
+        <v>1.7</v>
       </c>
       <c r="C8" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="D8" t="n">
-        <v>2.15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>6VWd5zF7</t>
+          <t>4rQsoH7m</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1</v>
+        <v>1.65</v>
       </c>
       <c r="C9" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>pGrl7dpe</t>
+          <t>n37VJZT0</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="C10" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="D10" t="n">
-        <v>1.95</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>06X4YYrf</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>hMoEUjrJ</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>KSw0hfzQ</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" t="n">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>YemQuHjK</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D14" t="n">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>4vvdzeEs</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>7</v>
-      </c>
-      <c r="C15" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>h0AwIDbD</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>jyEMLeal</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D17" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>4rQsoH7m</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D18" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>n37VJZT0</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>YJVCWCD6</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="C20" t="n">
-        <v>4</v>
-      </c>
-      <c r="D20" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>QmPfsURO</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>0AJjqex0</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>40FWnYcm</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>KApUeTtI</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>EB22wLQj</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>CQIvoCSa</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>4Ef51XCt</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>hzRnqjcC</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>YgnMckC5</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>CvbDaBsg</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,145 +448,81 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>06X4YYrf</t>
+          <t>h0AwIDbD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="C2" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="D2" t="n">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hMoEUjrJ</t>
+          <t>jyEMLeal</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="C3" t="n">
-        <v>2.88</v>
+        <v>3.7</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KSw0hfzQ</t>
+          <t>4rQsoH7m</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YemQuHjK</t>
+          <t>n37VJZT0</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="D5" t="n">
-        <v>4.75</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4vvdzeEs</t>
+          <t>YJVCWCD6</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>1.45</v>
       </c>
       <c r="C6" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="D6" t="n">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>h0AwIDbD</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>jyEMLeal</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>4rQsoH7m</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>n37VJZT0</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,81 +448,209 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>h0AwIDbD</t>
+          <t>QmPfsURO</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="C2" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jyEMLeal</t>
+          <t>0AJjqex0</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="C3" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>5.25</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4rQsoH7m</t>
+          <t>40FWnYcm</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="C4" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="D4" t="n">
-        <v>6.25</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>n37VJZT0</t>
+          <t>KApUeTtI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="C5" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YJVCWCD6</t>
+          <t>EB22wLQj</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.45</v>
+        <v>3.1</v>
       </c>
       <c r="C6" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>CQIvoCSa</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="C7" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>4Ef51XCt</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>hzRnqjcC</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>YgnMckC5</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>CvbDaBsg</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Gz9WD123</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>YNHbsZ6C</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>ll7vCuXF</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -448,209 +448,209 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>QmPfsURO</t>
+          <t>4Ef51XCt</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="C2" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0AJjqex0</t>
+          <t>hzRnqjcC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.1</v>
+        <v>5.25</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="D3" t="n">
-        <v>2.55</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>40FWnYcm</t>
+          <t>YgnMckC5</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="C4" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>KApUeTtI</t>
+          <t>CvbDaBsg</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="D5" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>EB22wLQj</t>
+          <t>Gz9WD123</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CQIvoCSa</t>
+          <t>YNHbsZ6C</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="C7" t="n">
-        <v>6.25</v>
+        <v>4.2</v>
       </c>
       <c r="D7" t="n">
-        <v>8.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
+          <t>ll7vCuXF</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="C8" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="D8" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>h2NyhKup</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.25</v>
+        <v>2.35</v>
       </c>
       <c r="C9" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="D9" t="n">
-        <v>1.57</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
+          <t>8Uo5ctIM</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.45</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
+          <t>0SQqjbAd</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="C11" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="D11" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>65kl1OIc</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="C12" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="D12" t="n">
-        <v>3.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="C13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D13" t="n">
         <v>4.1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="C14" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="D14" t="n">
-        <v>2.25</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,209 +448,321 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
+          <t>Gz9WD123</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="C2" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>YNHbsZ6C</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.25</v>
+        <v>1.5</v>
       </c>
       <c r="C3" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.55</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
+          <t>ll7vCuXF</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="C4" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
+          <t>h2NyhKup</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="C5" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="D5" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>8Uo5ctIM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.7</v>
+        <v>4.33</v>
       </c>
       <c r="C6" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="D6" t="n">
-        <v>3.9</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>0SQqjbAd</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="D7" t="n">
-        <v>5.25</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>65kl1OIc</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.7</v>
+        <v>1.33</v>
       </c>
       <c r="C8" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="D8" t="n">
-        <v>2.25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>h2NyhKup</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="C9" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="D9" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>8Uo5ctIM</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1.67</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>0SQqjbAd</t>
+          <t>QqTA4cPk</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="C11" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D11" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>65kl1OIc</t>
+          <t>vymauDyP</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="C12" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="D12" t="n">
-        <v>7.5</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>f1xuAJ1S</t>
+          <t>x88gL4RQ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="C13" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="D13" t="n">
-        <v>4.1</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2Xrca2mA</t>
+          <t>dhkQFrkl</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.3</v>
+        <v>2.15</v>
       </c>
       <c r="C14" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>8Sp1FEw8</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>4zlpJdvq</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>02sgHz9e</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>naHJ2yf2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>842EOIGL</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>jiAoNQdE</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>E595Qvn9</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="3">
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4">
@@ -506,7 +506,7 @@
         <v>3.4</v>
       </c>
       <c r="D5" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="6">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="C6" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="7">
@@ -535,10 +535,10 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="8">
@@ -583,7 +583,7 @@
         <v>1.3</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="C12" t="n">
         <v>3.5</v>
       </c>
       <c r="D12" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="C13" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="D13" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -644,13 +644,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -676,13 +676,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="D16" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="17">
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
         <v>3.2</v>
@@ -708,13 +708,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="C18" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D18" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="19">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="C19" t="n">
         <v>3.4</v>
       </c>
       <c r="D19" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="20">
@@ -740,13 +740,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="C20" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="D20" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="21">

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -468,10 +468,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="C3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="D3" t="n">
         <v>7.5</v>
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="C4" t="n">
         <v>3.4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="5">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="C6" t="n">
         <v>4.5</v>
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="C7" t="n">
         <v>3.1</v>
       </c>
       <c r="D7" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="C12" t="n">
         <v>3.5</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="13">
@@ -650,7 +650,7 @@
         <v>3.2</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="15">
@@ -714,7 +714,7 @@
         <v>3.3</v>
       </c>
       <c r="D18" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="19">
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
         <v>3.4</v>
@@ -740,13 +740,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="C20" t="n">
         <v>3.5</v>
       </c>
       <c r="D20" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="21">

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,321 +448,81 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>0SQqjbAd</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.25</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>65kl1OIc</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="C3" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="D3" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="C4" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D4" t="n">
-        <v>2.63</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h2NyhKup</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="C5" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8Uo5ctIM</t>
+          <t>QqTA4cPk</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.75</v>
+        <v>1.7</v>
       </c>
       <c r="C6" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>0SQqjbAd</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>65kl1OIc</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="C8" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="D8" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>f1xuAJ1S</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D9" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>2Xrca2mA</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C10" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="D10" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>QqTA4cPk</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D11" t="n">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>vymauDyP</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2.38</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>x88gL4RQ</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>dhkQFrkl</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>8Sp1FEw8</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>4zlpJdvq</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>02sgHz9e</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2.45</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>naHJ2yf2</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D18" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>842EOIGL</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>jiAoNQdE</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="C20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D20" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>E595Qvn9</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>3</v>
-      </c>
-      <c r="C21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2.5</v>
+        <v>5.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,81 +448,321 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0SQqjbAd</t>
+          <t>vymauDyP</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="C2" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>65kl1OIc</t>
+          <t>x88gL4RQ</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.33</v>
+        <v>3.5</v>
       </c>
       <c r="C3" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>f1xuAJ1S</t>
+          <t>dhkQFrkl</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="C4" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2Xrca2mA</t>
+          <t>8Sp1FEw8</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="C5" t="n">
-        <v>5.75</v>
+        <v>3.4</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>QqTA4cPk</t>
+          <t>4zlpJdvq</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>02sgHz9e</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>naHJ2yf2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>842EOIGL</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>jiAoNQdE</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>E595Qvn9</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>02cHDDPH</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>4z48FZf5</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>1.7</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>dA00HeQh</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YFePBifU</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C15" t="n">
         <v>3.7</v>
       </c>
-      <c r="D6" t="n">
-        <v>5.25</v>
+      <c r="D15" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>zHmSVfun</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QXtsC0lD</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>UaS8aGMt</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>rsizUY9b</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>U5mYDMJ0</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>zeCiJHet</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4.33</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="C2" t="n">
         <v>3.3</v>
@@ -471,7 +471,7 @@
         <v>3.5</v>
       </c>
       <c r="C3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -490,7 +490,7 @@
         <v>3.2</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="C5" t="n">
         <v>3.4</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="6">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="7">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="C7" t="n">
         <v>3.25</v>
       </c>
       <c r="D7" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="8">
@@ -551,10 +551,10 @@
         <v>2.2</v>
       </c>
       <c r="C8" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="9">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="D9" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="10">
@@ -586,7 +586,7 @@
         <v>3.6</v>
       </c>
       <c r="D10" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -596,173 +596,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="C11" t="n">
         <v>3.1</v>
       </c>
       <c r="D11" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>02cHDDPH</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>4z48FZf5</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D13" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>dA00HeQh</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D14" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>YFePBifU</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D15" t="n">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>zHmSVfun</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="C16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>QXtsC0lD</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="C17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>UaS8aGMt</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="C18" t="n">
-        <v>8</v>
-      </c>
-      <c r="D18" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>rsizUY9b</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>U5mYDMJ0</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="C20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D20" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>zeCiJHet</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="C21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D21" t="n">
-        <v>4.33</v>
+        <v>2.55</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,161 +448,321 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vymauDyP</t>
+          <t>02cHDDPH</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="C2" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>x88gL4RQ</t>
+          <t>4z48FZf5</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="C3" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dhkQFrkl</t>
+          <t>dA00HeQh</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="C4" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8Sp1FEw8</t>
+          <t>YFePBifU</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.9</v>
+        <v>1.73</v>
       </c>
       <c r="C5" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4zlpJdvq</t>
+          <t>zHmSVfun</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>6.5</v>
       </c>
       <c r="C6" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="D6" t="n">
-        <v>3.25</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>02sgHz9e</t>
+          <t>QXtsC0lD</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.25</v>
+        <v>1.27</v>
       </c>
       <c r="C7" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>naHJ2yf2</t>
+          <t>UaS8aGMt</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2</v>
+        <v>1.14</v>
       </c>
       <c r="C8" t="n">
-        <v>3.1</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>3.6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>842EOIGL</t>
+          <t>rsizUY9b</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="C9" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="D9" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>jiAoNQdE</t>
+          <t>U5mYDMJ0</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="C10" t="n">
         <v>3.6</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>E595Qvn9</t>
+          <t>zeCiJHet</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>rPc4X7Gj</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>nucZxUhT</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>bXuieB8c</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>jFGHcfig</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>2.9</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>CMriQj9N</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C16" t="n">
         <v>3.1</v>
       </c>
-      <c r="D11" t="n">
-        <v>2.55</v>
+      <c r="D16" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4duqSCvB</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Ia5ItCg4</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>UwPNKUWp</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>MXB9rYOi</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>QP8QvjOG</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.83</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="3">
@@ -471,10 +471,10 @@
         <v>1.6</v>
       </c>
       <c r="C3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="4">
@@ -484,285 +484,93 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="C4" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D4" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YFePBifU</t>
+          <t>QXtsC0lD</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.73</v>
+        <v>1.27</v>
       </c>
       <c r="C5" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>4.75</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zHmSVfun</t>
+          <t>UaS8aGMt</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.5</v>
+        <v>1.13</v>
       </c>
       <c r="C6" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>1.48</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>QXtsC0lD</t>
+          <t>rsizUY9b</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.27</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>UaS8aGMt</t>
+          <t>U5mYDMJ0</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.14</v>
+        <v>1.85</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>3.6</v>
       </c>
       <c r="D8" t="n">
-        <v>17</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>rsizUY9b</t>
+          <t>zeCiJHet</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="C9" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="D9" t="n">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>U5mYDMJ0</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D10" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>zeCiJHet</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D11" t="n">
         <v>4.33</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>rPc4X7Gj</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>nucZxUhT</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="C13" t="n">
-        <v>7</v>
-      </c>
-      <c r="D13" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>bXuieB8c</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="C14" t="n">
-        <v>4</v>
-      </c>
-      <c r="D14" t="n">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>jFGHcfig</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>CMriQj9N</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>4duqSCvB</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Ia5ItCg4</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>UwPNKUWp</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>MXB9rYOi</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>QP8QvjOG</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="C21" t="n">
-        <v>4</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.83</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,129 +448,161 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>02cHDDPH</t>
+          <t>rPc4X7Gj</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4z48FZf5</t>
+          <t>nucZxUhT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.6</v>
+        <v>1.18</v>
       </c>
       <c r="C3" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="D3" t="n">
-        <v>6.25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dA00HeQh</t>
+          <t>bXuieB8c</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="C4" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QXtsC0lD</t>
+          <t>jFGHcfig</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.27</v>
+        <v>2.63</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="D5" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>UaS8aGMt</t>
+          <t>UwPNKUWp</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.13</v>
+        <v>2.88</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rsizUY9b</t>
+          <t>4duqSCvB</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.55</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>U5mYDMJ0</t>
+          <t>Ia5ItCg4</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.85</v>
+        <v>3.3</v>
       </c>
       <c r="C8" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="D8" t="n">
-        <v>4.1</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zeCiJHet</t>
+          <t>CMriQj9N</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="C9" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="D9" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>MXB9rYOi</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>QP8QvjOG</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="C11" t="n">
         <v>4.33</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="C2" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="3">
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="C3" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -490,119 +490,183 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>jFGHcfig</t>
+          <t>UwPNKUWp</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="C5" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>UwPNKUWp</t>
+          <t>4duqSCvB</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="C6" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="D6" t="n">
-        <v>2.55</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4duqSCvB</t>
+          <t>Ia5ItCg4</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.95</v>
+        <v>3.4</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Ia5ItCg4</t>
+          <t>CMriQj9N</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="C8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D8" t="n">
         <v>3.1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2.35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CMriQj9N</t>
+          <t>MXB9rYOi</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.45</v>
+        <v>4.75</v>
       </c>
       <c r="C9" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="D9" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>MXB9rYOi</t>
+          <t>QP8QvjOG</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="C10" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>QP8QvjOG</t>
+          <t>SCX7iT7M</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.75</v>
+        <v>1.67</v>
       </c>
       <c r="C11" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.8</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>C2KEmK6l</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>vVwOqx6D</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>buKPeYL5</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IsCnpo0d</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.75</v>
       </c>
     </row>
   </sheetData>
